--- a/仓库与店铺对应关系表.xlsx
+++ b/仓库与店铺对应关系表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
   <si>
     <t>仓库</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>TX长沙</t>
+  </si>
+  <si>
+    <t>DAPHNE.LAB TX长沙直营店</t>
   </si>
 </sst>
 </file>
@@ -228,7 +231,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,6 +252,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -393,7 +401,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -516,12 +524,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -599,7 +601,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -660,6 +662,21 @@
       <top/>
       <bottom style="thin">
         <color rgb="FFA6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -781,137 +798,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -929,6 +946,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1455,7 +1475,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -1805,6 +1825,14 @@
         <v>62</v>
       </c>
     </row>
+    <row r="25" spans="1:6">
+      <c r="D25" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/仓库与店铺对应关系表.xlsx
+++ b/仓库与店铺对应关系表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="64">
   <si>
     <t>仓库</t>
   </si>
@@ -209,6 +209,9 @@
     <t>南京IST</t>
   </si>
   <si>
+    <t>DAPHNE.LAB TX长沙直营店</t>
+  </si>
+  <si>
     <t>TX淮海</t>
   </si>
   <si>
@@ -216,9 +219,6 @@
   </si>
   <si>
     <t>TX长沙</t>
-  </si>
-  <si>
-    <t>DAPHNE.LAB TX长沙直营店</t>
   </si>
 </sst>
 </file>
@@ -654,19 +654,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFA6A6A6"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFA6A6A6"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFA6A6A6"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
@@ -677,6 +664,19 @@
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA6A6A6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA6A6A6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFA6A6A6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -944,11 +944,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1800,11 +1800,17 @@
       <c r="F21" s="1"/>
     </row>
     <row r="22" spans="1:6">
+      <c r="A22" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="D22" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>60</v>
+      <c r="E22" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="F22" s="1"/>
     </row>
@@ -1813,7 +1819,7 @@
         <v>14</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F23" s="1"/>
     </row>
@@ -1822,15 +1828,15 @@
         <v>16</v>
       </c>
       <c r="E24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E25" t="s">
         <v>63</v>
-      </c>
-      <c r="E25" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
